--- a/AAII_Financials/Yearly/CLPR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CLPR_YR_FIN.xlsx
@@ -2973,10 +2973,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3075,10 +3075,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>18100</v>
+        <v>19800</v>
       </c>
       <c r="E60" s="3">
-        <v>18700</v>
+        <v>98700</v>
       </c>
       <c r="F60" s="3">
         <v>21000</v>
@@ -3126,10 +3126,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1277500</v>
+        <v>1275800</v>
       </c>
       <c r="E61" s="3">
-        <v>1266300</v>
+        <v>1186300</v>
       </c>
       <c r="F61" s="3">
         <v>1205600</v>
